--- a/Modelo_Pedido.xlsx
+++ b/Modelo_Pedido.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matheus\Desktop\formulario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3A622B-33C1-4F06-94BB-0F17ACB4B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{6C3A622B-33C1-4F06-94BB-0F17ACB4B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA49FF63-7F3F-4936-8B5C-82DF49FF28FE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="769" xr2:uid="{5A652F58-DF8E-46BE-9DBB-1F3AA7045651}"/>
+    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" tabRatio="769" xr2:uid="{5A652F58-DF8E-46BE-9DBB-1F3AA7045651}"/>
   </bookViews>
   <sheets>
     <sheet name="Pedido" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Pedido!$A$1:$F$92</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Pedido!$A$1:$G$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>DATA:</t>
   </si>
@@ -85,6 +85,9 @@
   <si>
     <t>ITEM</t>
   </si>
+  <si>
+    <t>DATA NECESSÁRIA</t>
+  </si>
 </sst>
 </file>
 
@@ -115,7 +118,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -333,11 +336,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -378,6 +420,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -402,11 +453,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,9 +490,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>885195</xdr:colOff>
+      <xdr:colOff>896625</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>617798</xdr:rowOff>
+      <xdr:rowOff>629228</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -798,7 +852,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519DEBFB-8826-4B53-A2FB-8FF5B4F0043B}">
   <sheetPr codeName="Planilha3"/>
-  <dimension ref="A1:F1048571"/>
+  <dimension ref="A1:G1048571"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -806,109 +860,113 @@
     <col min="3" max="3" width="43.109375" style="4" customWidth="1"/>
     <col min="4" max="4" width="5.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" customWidth="1"/>
+    <col min="6" max="7" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="F1" s="12"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="14"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="7"/>
       <c r="D3"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22"/>
+      <c r="B4" s="25"/>
       <c r="C4" s="9"/>
       <c r="D4"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="22"/>
+      <c r="B5" s="25"/>
       <c r="C5"/>
       <c r="D5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="14"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="6"/>
       <c r="D7"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="22"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="10"/>
       <c r="D8"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="22"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="6"/>
       <c r="D9"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="21" t="s">
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="22"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="6"/>
       <c r="D10"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>14</v>
       </c>
@@ -924,1013 +982,1116 @@
       <c r="E12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="30" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="1"/>
-      <c r="C13" s="26"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="11"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="27"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F13" s="31"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2</v>
       </c>
       <c r="B14" s="1"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="11"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="27"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="31"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>3</v>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="26"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="11"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="27"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F15" s="31"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>4</v>
       </c>
       <c r="B16" s="1"/>
-      <c r="C16" s="26"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="11"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="27"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F16" s="31"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>5</v>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="26"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="11"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="27"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F17" s="31"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>6</v>
       </c>
       <c r="B18" s="1"/>
-      <c r="C18" s="26"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="11"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="27"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F18" s="31"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>7</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="26"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="11"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="27"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F19" s="31"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>8</v>
       </c>
       <c r="B20" s="1"/>
-      <c r="C20" s="26"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="11"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="27"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F20" s="31"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>9</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" s="26"/>
+      <c r="C21" s="19"/>
       <c r="D21" s="11"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="27"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F21" s="31"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>10</v>
       </c>
       <c r="B22" s="1"/>
-      <c r="C22" s="26"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="11"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="27"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F22" s="31"/>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>11</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="26"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="11"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="27"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="31"/>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>12</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="26"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="11"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="27"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="31"/>
+      <c r="G24" s="20"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>13</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="C25" s="26"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="11"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="27"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F25" s="31"/>
+      <c r="G25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>14</v>
       </c>
       <c r="B26" s="1"/>
-      <c r="C26" s="26"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="11"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="27"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F26" s="31"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>15</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="26"/>
+      <c r="C27" s="19"/>
       <c r="D27" s="11"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="31"/>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>16</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="26"/>
+      <c r="C28" s="19"/>
       <c r="D28" s="11"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="27"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="31"/>
+      <c r="G28" s="20"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>17</v>
       </c>
       <c r="B29" s="1"/>
-      <c r="C29" s="26"/>
+      <c r="C29" s="19"/>
       <c r="D29" s="11"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="27"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F29" s="31"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>18</v>
       </c>
       <c r="B30" s="1"/>
-      <c r="C30" s="26"/>
+      <c r="C30" s="19"/>
       <c r="D30" s="11"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="27"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F30" s="31"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>19</v>
       </c>
       <c r="B31" s="1"/>
-      <c r="C31" s="26"/>
+      <c r="C31" s="19"/>
       <c r="D31" s="11"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="27"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F31" s="31"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>20</v>
       </c>
       <c r="B32" s="1"/>
-      <c r="C32" s="26"/>
+      <c r="C32" s="19"/>
       <c r="D32" s="11"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="27"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F32" s="31"/>
+      <c r="G32" s="20"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>21</v>
       </c>
       <c r="B33" s="1"/>
-      <c r="C33" s="26"/>
+      <c r="C33" s="19"/>
       <c r="D33" s="11"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="27"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F33" s="31"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>22</v>
       </c>
       <c r="B34" s="1"/>
-      <c r="C34" s="26"/>
+      <c r="C34" s="19"/>
       <c r="D34" s="11"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="27"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F34" s="31"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>23</v>
       </c>
       <c r="B35" s="1"/>
-      <c r="C35" s="26"/>
+      <c r="C35" s="19"/>
       <c r="D35" s="11"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="27"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="31"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>24</v>
       </c>
       <c r="B36" s="1"/>
-      <c r="C36" s="26"/>
+      <c r="C36" s="19"/>
       <c r="D36" s="11"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="27"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F36" s="31"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>25</v>
       </c>
       <c r="B37" s="1"/>
-      <c r="C37" s="26"/>
+      <c r="C37" s="19"/>
       <c r="D37" s="11"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="27"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37" s="31"/>
+      <c r="G37" s="20"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>26</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="26"/>
+      <c r="C38" s="19"/>
       <c r="D38" s="11"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="27"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38" s="31"/>
+      <c r="G38" s="20"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>27</v>
       </c>
       <c r="B39" s="1"/>
-      <c r="C39" s="26"/>
+      <c r="C39" s="19"/>
       <c r="D39" s="11"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="27"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="31"/>
+      <c r="G39" s="20"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>28</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="26"/>
+      <c r="C40" s="19"/>
       <c r="D40" s="11"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="27"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F40" s="31"/>
+      <c r="G40" s="20"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>29</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="26"/>
+      <c r="C41" s="19"/>
       <c r="D41" s="11"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="27"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F41" s="31"/>
+      <c r="G41" s="20"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>30</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="26"/>
+      <c r="C42" s="19"/>
       <c r="D42" s="11"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="27"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F42" s="31"/>
+      <c r="G42" s="20"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>31</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="26"/>
+      <c r="C43" s="19"/>
       <c r="D43" s="11"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="27"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" s="31"/>
+      <c r="G43" s="20"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>32</v>
       </c>
       <c r="B44" s="1"/>
-      <c r="C44" s="26"/>
+      <c r="C44" s="19"/>
       <c r="D44" s="11"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="27"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F44" s="31"/>
+      <c r="G44" s="20"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>33</v>
       </c>
       <c r="B45" s="1"/>
-      <c r="C45" s="26"/>
+      <c r="C45" s="19"/>
       <c r="D45" s="11"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="27"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F45" s="31"/>
+      <c r="G45" s="20"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>34</v>
       </c>
       <c r="B46" s="1"/>
-      <c r="C46" s="26"/>
+      <c r="C46" s="19"/>
       <c r="D46" s="11"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="27"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F46" s="31"/>
+      <c r="G46" s="20"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>35</v>
       </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="26"/>
+      <c r="C47" s="19"/>
       <c r="D47" s="11"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="27"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F47" s="31"/>
+      <c r="G47" s="20"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>36</v>
       </c>
       <c r="B48" s="1"/>
-      <c r="C48" s="26"/>
+      <c r="C48" s="19"/>
       <c r="D48" s="11"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="27"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F48" s="31"/>
+      <c r="G48" s="20"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>37</v>
       </c>
       <c r="B49" s="1"/>
-      <c r="C49" s="26"/>
+      <c r="C49" s="19"/>
       <c r="D49" s="11"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="27"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F49" s="31"/>
+      <c r="G49" s="20"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>38</v>
       </c>
       <c r="B50" s="1"/>
-      <c r="C50" s="26"/>
+      <c r="C50" s="19"/>
       <c r="D50" s="11"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="27"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F50" s="31"/>
+      <c r="G50" s="20"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>39</v>
       </c>
       <c r="B51" s="1"/>
-      <c r="C51" s="26"/>
+      <c r="C51" s="19"/>
       <c r="D51" s="11"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="27"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F51" s="31"/>
+      <c r="G51" s="20"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>40</v>
       </c>
       <c r="B52" s="1"/>
-      <c r="C52" s="26"/>
+      <c r="C52" s="19"/>
       <c r="D52" s="11"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="27"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F52" s="31"/>
+      <c r="G52" s="20"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>41</v>
       </c>
       <c r="B53" s="1"/>
-      <c r="C53" s="26"/>
+      <c r="C53" s="19"/>
       <c r="D53" s="11"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="27"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F53" s="31"/>
+      <c r="G53" s="20"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>42</v>
       </c>
       <c r="B54" s="1"/>
-      <c r="C54" s="26"/>
+      <c r="C54" s="19"/>
       <c r="D54" s="11"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="27"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F54" s="31"/>
+      <c r="G54" s="20"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>43</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="26"/>
+      <c r="C55" s="19"/>
       <c r="D55" s="11"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="27"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F55" s="31"/>
+      <c r="G55" s="20"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>44</v>
       </c>
       <c r="B56" s="1"/>
-      <c r="C56" s="26"/>
+      <c r="C56" s="19"/>
       <c r="D56" s="11"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="27"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F56" s="31"/>
+      <c r="G56" s="20"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>45</v>
       </c>
       <c r="B57" s="1"/>
-      <c r="C57" s="26"/>
+      <c r="C57" s="19"/>
       <c r="D57" s="11"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="27"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F57" s="31"/>
+      <c r="G57" s="20"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>46</v>
       </c>
       <c r="B58" s="1"/>
-      <c r="C58" s="26"/>
+      <c r="C58" s="19"/>
       <c r="D58" s="11"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="27"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F58" s="31"/>
+      <c r="G58" s="20"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>47</v>
       </c>
       <c r="B59" s="1"/>
-      <c r="C59" s="26"/>
+      <c r="C59" s="19"/>
       <c r="D59" s="11"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="27"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F59" s="31"/>
+      <c r="G59" s="20"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>48</v>
       </c>
       <c r="B60" s="1"/>
-      <c r="C60" s="26"/>
+      <c r="C60" s="19"/>
       <c r="D60" s="11"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="27"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F60" s="31"/>
+      <c r="G60" s="20"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>49</v>
       </c>
       <c r="B61" s="1"/>
-      <c r="C61" s="26"/>
+      <c r="C61" s="19"/>
       <c r="D61" s="11"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="27"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F61" s="31"/>
+      <c r="G61" s="20"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>50</v>
       </c>
       <c r="B62" s="1"/>
-      <c r="C62" s="26"/>
+      <c r="C62" s="19"/>
       <c r="D62" s="11"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="27"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F62" s="31"/>
+      <c r="G62" s="20"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>51</v>
       </c>
       <c r="B63" s="1"/>
-      <c r="C63" s="26"/>
+      <c r="C63" s="19"/>
       <c r="D63" s="11"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="27"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F63" s="31"/>
+      <c r="G63" s="20"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>52</v>
       </c>
       <c r="B64" s="1"/>
-      <c r="C64" s="26"/>
+      <c r="C64" s="19"/>
       <c r="D64" s="11"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="27"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F64" s="31"/>
+      <c r="G64" s="20"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>53</v>
       </c>
       <c r="B65" s="1"/>
-      <c r="C65" s="26"/>
+      <c r="C65" s="19"/>
       <c r="D65" s="11"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="27"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F65" s="31"/>
+      <c r="G65" s="20"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>54</v>
       </c>
       <c r="B66" s="1"/>
-      <c r="C66" s="26"/>
+      <c r="C66" s="19"/>
       <c r="D66" s="11"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="27"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F66" s="31"/>
+      <c r="G66" s="20"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>55</v>
       </c>
       <c r="B67" s="1"/>
-      <c r="C67" s="26"/>
+      <c r="C67" s="19"/>
       <c r="D67" s="11"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="27"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F67" s="31"/>
+      <c r="G67" s="20"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>56</v>
       </c>
       <c r="B68" s="1"/>
-      <c r="C68" s="26"/>
+      <c r="C68" s="19"/>
       <c r="D68" s="11"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="27"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F68" s="31"/>
+      <c r="G68" s="20"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>57</v>
       </c>
       <c r="B69" s="1"/>
-      <c r="C69" s="26"/>
+      <c r="C69" s="19"/>
       <c r="D69" s="11"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="27"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F69" s="31"/>
+      <c r="G69" s="20"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>58</v>
       </c>
       <c r="B70" s="1"/>
-      <c r="C70" s="26"/>
+      <c r="C70" s="19"/>
       <c r="D70" s="11"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="27"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F70" s="31"/>
+      <c r="G70" s="20"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>59</v>
       </c>
       <c r="B71" s="1"/>
-      <c r="C71" s="26"/>
+      <c r="C71" s="19"/>
       <c r="D71" s="11"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="27"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F71" s="31"/>
+      <c r="G71" s="20"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>60</v>
       </c>
       <c r="B72" s="1"/>
-      <c r="C72" s="26"/>
+      <c r="C72" s="19"/>
       <c r="D72" s="11"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="27"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F72" s="31"/>
+      <c r="G72" s="20"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>61</v>
       </c>
       <c r="B73" s="1"/>
-      <c r="C73" s="26"/>
+      <c r="C73" s="19"/>
       <c r="D73" s="11"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="27"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F73" s="31"/>
+      <c r="G73" s="20"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>62</v>
       </c>
       <c r="B74" s="1"/>
-      <c r="C74" s="26"/>
+      <c r="C74" s="19"/>
       <c r="D74" s="11"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="27"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F74" s="31"/>
+      <c r="G74" s="20"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>63</v>
       </c>
       <c r="B75" s="1"/>
-      <c r="C75" s="26"/>
+      <c r="C75" s="19"/>
       <c r="D75" s="11"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="27"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F75" s="31"/>
+      <c r="G75" s="20"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>64</v>
       </c>
       <c r="B76" s="1"/>
-      <c r="C76" s="26"/>
+      <c r="C76" s="19"/>
       <c r="D76" s="11"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="27"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F76" s="31"/>
+      <c r="G76" s="20"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>65</v>
       </c>
       <c r="B77" s="1"/>
-      <c r="C77" s="26"/>
+      <c r="C77" s="19"/>
       <c r="D77" s="11"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="27"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F77" s="31"/>
+      <c r="G77" s="20"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>66</v>
       </c>
       <c r="B78" s="1"/>
-      <c r="C78" s="26"/>
+      <c r="C78" s="19"/>
       <c r="D78" s="11"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="27"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F78" s="31"/>
+      <c r="G78" s="20"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>67</v>
       </c>
       <c r="B79" s="1"/>
-      <c r="C79" s="26"/>
+      <c r="C79" s="19"/>
       <c r="D79" s="11"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="27"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F79" s="31"/>
+      <c r="G79" s="20"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>68</v>
       </c>
       <c r="B80" s="1"/>
-      <c r="C80" s="26"/>
+      <c r="C80" s="19"/>
       <c r="D80" s="11"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="27"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F80" s="31"/>
+      <c r="G80" s="20"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>69</v>
       </c>
       <c r="B81" s="1"/>
-      <c r="C81" s="26"/>
+      <c r="C81" s="19"/>
       <c r="D81" s="11"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="27"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F81" s="31"/>
+      <c r="G81" s="20"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>70</v>
       </c>
       <c r="B82" s="1"/>
-      <c r="C82" s="26"/>
+      <c r="C82" s="19"/>
       <c r="D82" s="11"/>
       <c r="E82" s="1"/>
-      <c r="F82" s="27"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F82" s="31"/>
+      <c r="G82" s="20"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>71</v>
       </c>
       <c r="B83" s="1"/>
-      <c r="C83" s="26"/>
+      <c r="C83" s="19"/>
       <c r="D83" s="11"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="27"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F83" s="31"/>
+      <c r="G83" s="20"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>72</v>
       </c>
       <c r="B84" s="1"/>
-      <c r="C84" s="26"/>
+      <c r="C84" s="19"/>
       <c r="D84" s="11"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="27"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F84" s="31"/>
+      <c r="G84" s="20"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>73</v>
       </c>
       <c r="B85" s="1"/>
-      <c r="C85" s="26"/>
+      <c r="C85" s="19"/>
       <c r="D85" s="11"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="27"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F85" s="31"/>
+      <c r="G85" s="20"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>74</v>
       </c>
       <c r="B86" s="1"/>
-      <c r="C86" s="26"/>
+      <c r="C86" s="19"/>
       <c r="D86" s="11"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="27"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F86" s="31"/>
+      <c r="G86" s="20"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>75</v>
       </c>
       <c r="B87" s="1"/>
-      <c r="C87" s="26"/>
+      <c r="C87" s="19"/>
       <c r="D87" s="11"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="27"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F87" s="31"/>
+      <c r="G87" s="20"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>76</v>
       </c>
       <c r="B88" s="1"/>
-      <c r="C88" s="26"/>
+      <c r="C88" s="19"/>
       <c r="D88" s="11"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="27"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F88" s="31"/>
+      <c r="G88" s="20"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>77</v>
       </c>
       <c r="B89" s="1"/>
-      <c r="C89" s="26"/>
+      <c r="C89" s="19"/>
       <c r="D89" s="11"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="27"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F89" s="31"/>
+      <c r="G89" s="20"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>78</v>
       </c>
       <c r="B90" s="1"/>
-      <c r="C90" s="26"/>
+      <c r="C90" s="19"/>
       <c r="D90" s="11"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="27"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F90" s="31"/>
+      <c r="G90" s="20"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>79</v>
       </c>
       <c r="B91" s="1"/>
-      <c r="C91" s="26"/>
+      <c r="C91" s="19"/>
       <c r="D91" s="11"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="27"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F91" s="31"/>
+      <c r="G91" s="20"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>80</v>
       </c>
       <c r="B92" s="1"/>
-      <c r="C92" s="26"/>
+      <c r="C92" s="19"/>
       <c r="D92" s="11"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="27"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F92" s="31"/>
+      <c r="G92" s="20"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>81</v>
       </c>
       <c r="B93" s="1"/>
-      <c r="C93" s="26"/>
+      <c r="C93" s="19"/>
       <c r="D93" s="11"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="27"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F93" s="31"/>
+      <c r="G93" s="20"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>82</v>
       </c>
       <c r="B94" s="1"/>
-      <c r="C94" s="26"/>
+      <c r="C94" s="19"/>
       <c r="D94" s="11"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="27"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F94" s="31"/>
+      <c r="G94" s="20"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>82</v>
       </c>
       <c r="B95" s="1"/>
-      <c r="C95" s="26"/>
+      <c r="C95" s="19"/>
       <c r="D95" s="11"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="27"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F95" s="31"/>
+      <c r="G95" s="20"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>84</v>
       </c>
       <c r="B96" s="1"/>
-      <c r="C96" s="26"/>
+      <c r="C96" s="19"/>
       <c r="D96" s="11"/>
       <c r="E96" s="1"/>
-      <c r="F96" s="27"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F96" s="31"/>
+      <c r="G96" s="20"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>85</v>
       </c>
       <c r="B97" s="1"/>
-      <c r="C97" s="26"/>
+      <c r="C97" s="19"/>
       <c r="D97" s="11"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="27"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F97" s="31"/>
+      <c r="G97" s="20"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>86</v>
       </c>
       <c r="B98" s="1"/>
-      <c r="C98" s="26"/>
+      <c r="C98" s="19"/>
       <c r="D98" s="11"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="27"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F98" s="31"/>
+      <c r="G98" s="20"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>87</v>
       </c>
       <c r="B99" s="1"/>
-      <c r="C99" s="26"/>
+      <c r="C99" s="19"/>
       <c r="D99" s="11"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="27"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F99" s="31"/>
+      <c r="G99" s="20"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>88</v>
       </c>
       <c r="B100" s="1"/>
-      <c r="C100" s="26"/>
+      <c r="C100" s="19"/>
       <c r="D100" s="11"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="27"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F100" s="31"/>
+      <c r="G100" s="20"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>89</v>
       </c>
       <c r="B101" s="1"/>
-      <c r="C101" s="26"/>
+      <c r="C101" s="19"/>
       <c r="D101" s="11"/>
       <c r="E101" s="1"/>
-      <c r="F101" s="27"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F101" s="31"/>
+      <c r="G101" s="20"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>90</v>
       </c>
       <c r="B102" s="1"/>
-      <c r="C102" s="26"/>
+      <c r="C102" s="19"/>
       <c r="D102" s="11"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="27"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F102" s="31"/>
+      <c r="G102" s="20"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>91</v>
       </c>
       <c r="B103" s="1"/>
-      <c r="C103" s="26"/>
+      <c r="C103" s="19"/>
       <c r="D103" s="11"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="27"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F103" s="31"/>
+      <c r="G103" s="20"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>92</v>
       </c>
       <c r="B104" s="1"/>
-      <c r="C104" s="26"/>
+      <c r="C104" s="19"/>
       <c r="D104" s="11"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="27"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F104" s="31"/>
+      <c r="G104" s="20"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>93</v>
       </c>
       <c r="B105" s="1"/>
-      <c r="C105" s="26"/>
+      <c r="C105" s="19"/>
       <c r="D105" s="11"/>
       <c r="E105" s="1"/>
-      <c r="F105" s="27"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F105" s="31"/>
+      <c r="G105" s="20"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>94</v>
       </c>
       <c r="B106" s="1"/>
-      <c r="C106" s="26"/>
+      <c r="C106" s="19"/>
       <c r="D106" s="11"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="27"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F106" s="31"/>
+      <c r="G106" s="20"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>95</v>
       </c>
       <c r="B107" s="1"/>
-      <c r="C107" s="26"/>
+      <c r="C107" s="19"/>
       <c r="D107" s="11"/>
       <c r="E107" s="1"/>
-      <c r="F107" s="27"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F107" s="31"/>
+      <c r="G107" s="20"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>96</v>
       </c>
       <c r="B108" s="1"/>
-      <c r="C108" s="26"/>
+      <c r="C108" s="19"/>
       <c r="D108" s="11"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="27"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F108" s="31"/>
+      <c r="G108" s="20"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>97</v>
       </c>
       <c r="B109" s="1"/>
-      <c r="C109" s="26"/>
+      <c r="C109" s="19"/>
       <c r="D109" s="11"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="27"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F109" s="31"/>
+      <c r="G109" s="20"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>98</v>
       </c>
       <c r="B110" s="1"/>
-      <c r="C110" s="26"/>
+      <c r="C110" s="19"/>
       <c r="D110" s="11"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="27"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F110" s="31"/>
+      <c r="G110" s="20"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>99</v>
       </c>
       <c r="B111" s="1"/>
-      <c r="C111" s="26"/>
+      <c r="C111" s="19"/>
       <c r="D111" s="11"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="27"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F111" s="31"/>
+      <c r="G111" s="20"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>100</v>
       </c>
       <c r="B112" s="1"/>
-      <c r="C112" s="26"/>
+      <c r="C112" s="19"/>
       <c r="D112" s="11"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="27"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="20"/>
     </row>
     <row r="1048571" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C1048571" s="20"/>
-      <c r="D1048571" s="20"/>
+      <c r="C1048571" s="23"/>
+      <c r="D1048571" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1940,7 +2101,7 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>

--- a/Modelo_Pedido.xlsx
+++ b/Modelo_Pedido.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{6C3A622B-33C1-4F06-94BB-0F17ACB4B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA49FF63-7F3F-4936-8B5C-82DF49FF28FE}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{6C3A622B-33C1-4F06-94BB-0F17ACB4B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{982554BE-3962-478F-8363-23FDD4A674FC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" tabRatio="769" xr2:uid="{5A652F58-DF8E-46BE-9DBB-1F3AA7045651}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="769" xr2:uid="{5A652F58-DF8E-46BE-9DBB-1F3AA7045651}"/>
   </bookViews>
   <sheets>
     <sheet name="Pedido" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Pedido!$A$1:$G$92</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Pedido!$A$1:$H$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>DATA:</t>
   </si>
@@ -86,7 +86,10 @@
     <t>ITEM</t>
   </si>
   <si>
-    <t>DATA NECESSÁRIA</t>
+    <t>DATA DE NECESSIDADE</t>
+  </si>
+  <si>
+    <t>MOTIVO DA URGÊNCIA</t>
   </si>
 </sst>
 </file>
@@ -429,6 +432,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -450,16 +459,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -852,7 +855,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519DEBFB-8826-4B53-A2FB-8FF5B4F0043B}">
   <sheetPr codeName="Planilha3"/>
-  <dimension ref="A1:G1048571"/>
+  <dimension ref="A1:H1048571"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -860,113 +863,119 @@
     <col min="3" max="3" width="43.109375" style="4" customWidth="1"/>
     <col min="4" max="4" width="5.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="G2" s="18"/>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="7"/>
       <c r="D3"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="25"/>
+      <c r="B4" s="27"/>
       <c r="C4" s="9"/>
       <c r="D4"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="27"/>
       <c r="C5"/>
       <c r="D5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="G6" s="18"/>
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="6"/>
       <c r="D7"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="25"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="10"/>
       <c r="D8"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="6"/>
       <c r="D9"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="25"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="6"/>
       <c r="D10"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="28"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>14</v>
       </c>
@@ -982,14 +991,17 @@
       <c r="E12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -997,10 +1009,11 @@
       <c r="C13" s="19"/>
       <c r="D13" s="11"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2</v>
       </c>
@@ -1008,10 +1021,11 @@
       <c r="C14" s="19"/>
       <c r="D14" s="11"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="20"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>3</v>
       </c>
@@ -1019,10 +1033,11 @@
       <c r="C15" s="19"/>
       <c r="D15" s="11"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>4</v>
       </c>
@@ -1030,10 +1045,11 @@
       <c r="C16" s="19"/>
       <c r="D16" s="11"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>5</v>
       </c>
@@ -1041,10 +1057,11 @@
       <c r="C17" s="19"/>
       <c r="D17" s="11"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>6</v>
       </c>
@@ -1052,10 +1069,11 @@
       <c r="C18" s="19"/>
       <c r="D18" s="11"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="20"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="20"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>7</v>
       </c>
@@ -1063,10 +1081,11 @@
       <c r="C19" s="19"/>
       <c r="D19" s="11"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="20"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>8</v>
       </c>
@@ -1074,10 +1093,11 @@
       <c r="C20" s="19"/>
       <c r="D20" s="11"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="20"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>9</v>
       </c>
@@ -1085,10 +1105,11 @@
       <c r="C21" s="19"/>
       <c r="D21" s="11"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="20"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>10</v>
       </c>
@@ -1096,10 +1117,11 @@
       <c r="C22" s="19"/>
       <c r="D22" s="11"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>11</v>
       </c>
@@ -1107,10 +1129,11 @@
       <c r="C23" s="19"/>
       <c r="D23" s="11"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="20"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>12</v>
       </c>
@@ -1118,10 +1141,11 @@
       <c r="C24" s="19"/>
       <c r="D24" s="11"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="20"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>13</v>
       </c>
@@ -1129,10 +1153,11 @@
       <c r="C25" s="19"/>
       <c r="D25" s="11"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="20"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>14</v>
       </c>
@@ -1140,10 +1165,11 @@
       <c r="C26" s="19"/>
       <c r="D26" s="11"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="20"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="20"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>15</v>
       </c>
@@ -1151,10 +1177,11 @@
       <c r="C27" s="19"/>
       <c r="D27" s="11"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="20"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>16</v>
       </c>
@@ -1162,10 +1189,11 @@
       <c r="C28" s="19"/>
       <c r="D28" s="11"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="20"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>17</v>
       </c>
@@ -1173,10 +1201,11 @@
       <c r="C29" s="19"/>
       <c r="D29" s="11"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>18</v>
       </c>
@@ -1184,10 +1213,11 @@
       <c r="C30" s="19"/>
       <c r="D30" s="11"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="20"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>19</v>
       </c>
@@ -1195,10 +1225,11 @@
       <c r="C31" s="19"/>
       <c r="D31" s="11"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="20"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>20</v>
       </c>
@@ -1206,10 +1237,11 @@
       <c r="C32" s="19"/>
       <c r="D32" s="11"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="20"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="20"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>21</v>
       </c>
@@ -1217,10 +1249,11 @@
       <c r="C33" s="19"/>
       <c r="D33" s="11"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="20"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="20"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>22</v>
       </c>
@@ -1228,10 +1261,11 @@
       <c r="C34" s="19"/>
       <c r="D34" s="11"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="20"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="20"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>23</v>
       </c>
@@ -1239,10 +1273,11 @@
       <c r="C35" s="19"/>
       <c r="D35" s="11"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="20"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="20"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>24</v>
       </c>
@@ -1250,10 +1285,11 @@
       <c r="C36" s="19"/>
       <c r="D36" s="11"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="20"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="20"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>25</v>
       </c>
@@ -1261,10 +1297,11 @@
       <c r="C37" s="19"/>
       <c r="D37" s="11"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="20"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="20"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>26</v>
       </c>
@@ -1272,10 +1309,11 @@
       <c r="C38" s="19"/>
       <c r="D38" s="11"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="20"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="20"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>27</v>
       </c>
@@ -1283,10 +1321,11 @@
       <c r="C39" s="19"/>
       <c r="D39" s="11"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="20"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="20"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>28</v>
       </c>
@@ -1294,10 +1333,11 @@
       <c r="C40" s="19"/>
       <c r="D40" s="11"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="20"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="20"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>29</v>
       </c>
@@ -1305,10 +1345,11 @@
       <c r="C41" s="19"/>
       <c r="D41" s="11"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="20"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="20"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>30</v>
       </c>
@@ -1316,10 +1357,11 @@
       <c r="C42" s="19"/>
       <c r="D42" s="11"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="20"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="20"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>31</v>
       </c>
@@ -1327,10 +1369,11 @@
       <c r="C43" s="19"/>
       <c r="D43" s="11"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="20"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="20"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>32</v>
       </c>
@@ -1338,10 +1381,11 @@
       <c r="C44" s="19"/>
       <c r="D44" s="11"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="20"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="20"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>33</v>
       </c>
@@ -1349,10 +1393,11 @@
       <c r="C45" s="19"/>
       <c r="D45" s="11"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="20"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="20"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>34</v>
       </c>
@@ -1360,10 +1405,11 @@
       <c r="C46" s="19"/>
       <c r="D46" s="11"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="20"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="20"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>35</v>
       </c>
@@ -1371,10 +1417,11 @@
       <c r="C47" s="19"/>
       <c r="D47" s="11"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="20"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="20"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>36</v>
       </c>
@@ -1382,10 +1429,11 @@
       <c r="C48" s="19"/>
       <c r="D48" s="11"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="20"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="20"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>37</v>
       </c>
@@ -1393,10 +1441,11 @@
       <c r="C49" s="19"/>
       <c r="D49" s="11"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="20"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="20"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>38</v>
       </c>
@@ -1404,10 +1453,11 @@
       <c r="C50" s="19"/>
       <c r="D50" s="11"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="20"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="20"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>39</v>
       </c>
@@ -1415,10 +1465,11 @@
       <c r="C51" s="19"/>
       <c r="D51" s="11"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="20"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="20"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>40</v>
       </c>
@@ -1426,10 +1477,11 @@
       <c r="C52" s="19"/>
       <c r="D52" s="11"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="20"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="20"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>41</v>
       </c>
@@ -1437,10 +1489,11 @@
       <c r="C53" s="19"/>
       <c r="D53" s="11"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="20"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="20"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>42</v>
       </c>
@@ -1448,10 +1501,11 @@
       <c r="C54" s="19"/>
       <c r="D54" s="11"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="20"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="20"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>43</v>
       </c>
@@ -1459,10 +1513,11 @@
       <c r="C55" s="19"/>
       <c r="D55" s="11"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="20"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="20"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>44</v>
       </c>
@@ -1470,10 +1525,11 @@
       <c r="C56" s="19"/>
       <c r="D56" s="11"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="20"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="20"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>45</v>
       </c>
@@ -1481,10 +1537,11 @@
       <c r="C57" s="19"/>
       <c r="D57" s="11"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="20"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="20"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>46</v>
       </c>
@@ -1492,10 +1549,11 @@
       <c r="C58" s="19"/>
       <c r="D58" s="11"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="20"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="20"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>47</v>
       </c>
@@ -1503,10 +1561,11 @@
       <c r="C59" s="19"/>
       <c r="D59" s="11"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="20"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="20"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>48</v>
       </c>
@@ -1514,10 +1573,11 @@
       <c r="C60" s="19"/>
       <c r="D60" s="11"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="20"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="20"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>49</v>
       </c>
@@ -1525,10 +1585,11 @@
       <c r="C61" s="19"/>
       <c r="D61" s="11"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="20"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="20"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>50</v>
       </c>
@@ -1536,10 +1597,11 @@
       <c r="C62" s="19"/>
       <c r="D62" s="11"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="20"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="20"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>51</v>
       </c>
@@ -1547,10 +1609,11 @@
       <c r="C63" s="19"/>
       <c r="D63" s="11"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="20"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="20"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>52</v>
       </c>
@@ -1558,10 +1621,11 @@
       <c r="C64" s="19"/>
       <c r="D64" s="11"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="20"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="20"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>53</v>
       </c>
@@ -1569,10 +1633,11 @@
       <c r="C65" s="19"/>
       <c r="D65" s="11"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="20"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="20"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>54</v>
       </c>
@@ -1580,10 +1645,11 @@
       <c r="C66" s="19"/>
       <c r="D66" s="11"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="20"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="20"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>55</v>
       </c>
@@ -1591,10 +1657,11 @@
       <c r="C67" s="19"/>
       <c r="D67" s="11"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="20"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="20"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>56</v>
       </c>
@@ -1602,10 +1669,11 @@
       <c r="C68" s="19"/>
       <c r="D68" s="11"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="20"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="20"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>57</v>
       </c>
@@ -1613,10 +1681,11 @@
       <c r="C69" s="19"/>
       <c r="D69" s="11"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="20"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="20"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>58</v>
       </c>
@@ -1624,10 +1693,11 @@
       <c r="C70" s="19"/>
       <c r="D70" s="11"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="20"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="20"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>59</v>
       </c>
@@ -1635,10 +1705,11 @@
       <c r="C71" s="19"/>
       <c r="D71" s="11"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="20"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="20"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>60</v>
       </c>
@@ -1646,10 +1717,11 @@
       <c r="C72" s="19"/>
       <c r="D72" s="11"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="20"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="20"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>61</v>
       </c>
@@ -1657,10 +1729,11 @@
       <c r="C73" s="19"/>
       <c r="D73" s="11"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="20"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="20"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>62</v>
       </c>
@@ -1668,10 +1741,11 @@
       <c r="C74" s="19"/>
       <c r="D74" s="11"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="31"/>
-      <c r="G74" s="20"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="20"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>63</v>
       </c>
@@ -1679,10 +1753,11 @@
       <c r="C75" s="19"/>
       <c r="D75" s="11"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="20"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="20"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>64</v>
       </c>
@@ -1690,10 +1765,11 @@
       <c r="C76" s="19"/>
       <c r="D76" s="11"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="31"/>
-      <c r="G76" s="20"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="20"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>65</v>
       </c>
@@ -1701,10 +1777,11 @@
       <c r="C77" s="19"/>
       <c r="D77" s="11"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="20"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="20"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>66</v>
       </c>
@@ -1712,10 +1789,11 @@
       <c r="C78" s="19"/>
       <c r="D78" s="11"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="31"/>
-      <c r="G78" s="20"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="20"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>67</v>
       </c>
@@ -1723,10 +1801,11 @@
       <c r="C79" s="19"/>
       <c r="D79" s="11"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="20"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="20"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>68</v>
       </c>
@@ -1734,10 +1813,11 @@
       <c r="C80" s="19"/>
       <c r="D80" s="11"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="31"/>
-      <c r="G80" s="20"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>69</v>
       </c>
@@ -1745,10 +1825,11 @@
       <c r="C81" s="19"/>
       <c r="D81" s="11"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="31"/>
-      <c r="G81" s="20"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="20"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>70</v>
       </c>
@@ -1756,10 +1837,11 @@
       <c r="C82" s="19"/>
       <c r="D82" s="11"/>
       <c r="E82" s="1"/>
-      <c r="F82" s="31"/>
-      <c r="G82" s="20"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="20"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>71</v>
       </c>
@@ -1767,10 +1849,11 @@
       <c r="C83" s="19"/>
       <c r="D83" s="11"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="20"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="20"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>72</v>
       </c>
@@ -1778,10 +1861,11 @@
       <c r="C84" s="19"/>
       <c r="D84" s="11"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="31"/>
-      <c r="G84" s="20"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="20"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>73</v>
       </c>
@@ -1789,10 +1873,11 @@
       <c r="C85" s="19"/>
       <c r="D85" s="11"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="31"/>
-      <c r="G85" s="20"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="20"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>74</v>
       </c>
@@ -1800,10 +1885,11 @@
       <c r="C86" s="19"/>
       <c r="D86" s="11"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="20"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="20"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>75</v>
       </c>
@@ -1811,10 +1897,11 @@
       <c r="C87" s="19"/>
       <c r="D87" s="11"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="20"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="20"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>76</v>
       </c>
@@ -1822,10 +1909,11 @@
       <c r="C88" s="19"/>
       <c r="D88" s="11"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="31"/>
-      <c r="G88" s="20"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="20"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>77</v>
       </c>
@@ -1833,10 +1921,11 @@
       <c r="C89" s="19"/>
       <c r="D89" s="11"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="31"/>
-      <c r="G89" s="20"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="20"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>78</v>
       </c>
@@ -1844,10 +1933,11 @@
       <c r="C90" s="19"/>
       <c r="D90" s="11"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="31"/>
-      <c r="G90" s="20"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F90" s="22"/>
+      <c r="G90" s="22"/>
+      <c r="H90" s="20"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>79</v>
       </c>
@@ -1855,10 +1945,11 @@
       <c r="C91" s="19"/>
       <c r="D91" s="11"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="31"/>
-      <c r="G91" s="20"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F91" s="22"/>
+      <c r="G91" s="22"/>
+      <c r="H91" s="20"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>80</v>
       </c>
@@ -1866,10 +1957,11 @@
       <c r="C92" s="19"/>
       <c r="D92" s="11"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="31"/>
-      <c r="G92" s="20"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="20"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>81</v>
       </c>
@@ -1877,10 +1969,11 @@
       <c r="C93" s="19"/>
       <c r="D93" s="11"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="31"/>
-      <c r="G93" s="20"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
+      <c r="H93" s="20"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>82</v>
       </c>
@@ -1888,10 +1981,11 @@
       <c r="C94" s="19"/>
       <c r="D94" s="11"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="31"/>
-      <c r="G94" s="20"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="20"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>82</v>
       </c>
@@ -1899,10 +1993,11 @@
       <c r="C95" s="19"/>
       <c r="D95" s="11"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="31"/>
-      <c r="G95" s="20"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F95" s="22"/>
+      <c r="G95" s="22"/>
+      <c r="H95" s="20"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>84</v>
       </c>
@@ -1910,10 +2005,11 @@
       <c r="C96" s="19"/>
       <c r="D96" s="11"/>
       <c r="E96" s="1"/>
-      <c r="F96" s="31"/>
-      <c r="G96" s="20"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
+      <c r="H96" s="20"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>85</v>
       </c>
@@ -1921,10 +2017,11 @@
       <c r="C97" s="19"/>
       <c r="D97" s="11"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="31"/>
-      <c r="G97" s="20"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="20"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>86</v>
       </c>
@@ -1932,10 +2029,11 @@
       <c r="C98" s="19"/>
       <c r="D98" s="11"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="31"/>
-      <c r="G98" s="20"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="20"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>87</v>
       </c>
@@ -1943,10 +2041,11 @@
       <c r="C99" s="19"/>
       <c r="D99" s="11"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="31"/>
-      <c r="G99" s="20"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F99" s="22"/>
+      <c r="G99" s="22"/>
+      <c r="H99" s="20"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>88</v>
       </c>
@@ -1954,10 +2053,11 @@
       <c r="C100" s="19"/>
       <c r="D100" s="11"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="20"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F100" s="22"/>
+      <c r="G100" s="22"/>
+      <c r="H100" s="20"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>89</v>
       </c>
@@ -1965,10 +2065,11 @@
       <c r="C101" s="19"/>
       <c r="D101" s="11"/>
       <c r="E101" s="1"/>
-      <c r="F101" s="31"/>
-      <c r="G101" s="20"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="20"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>90</v>
       </c>
@@ -1976,10 +2077,11 @@
       <c r="C102" s="19"/>
       <c r="D102" s="11"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="31"/>
-      <c r="G102" s="20"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
+      <c r="H102" s="20"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>91</v>
       </c>
@@ -1987,10 +2089,11 @@
       <c r="C103" s="19"/>
       <c r="D103" s="11"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="31"/>
-      <c r="G103" s="20"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F103" s="22"/>
+      <c r="G103" s="22"/>
+      <c r="H103" s="20"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>92</v>
       </c>
@@ -1998,10 +2101,11 @@
       <c r="C104" s="19"/>
       <c r="D104" s="11"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="31"/>
-      <c r="G104" s="20"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F104" s="22"/>
+      <c r="G104" s="22"/>
+      <c r="H104" s="20"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>93</v>
       </c>
@@ -2009,10 +2113,11 @@
       <c r="C105" s="19"/>
       <c r="D105" s="11"/>
       <c r="E105" s="1"/>
-      <c r="F105" s="31"/>
-      <c r="G105" s="20"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F105" s="22"/>
+      <c r="G105" s="22"/>
+      <c r="H105" s="20"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>94</v>
       </c>
@@ -2020,10 +2125,11 @@
       <c r="C106" s="19"/>
       <c r="D106" s="11"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="31"/>
-      <c r="G106" s="20"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F106" s="22"/>
+      <c r="G106" s="22"/>
+      <c r="H106" s="20"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>95</v>
       </c>
@@ -2031,10 +2137,11 @@
       <c r="C107" s="19"/>
       <c r="D107" s="11"/>
       <c r="E107" s="1"/>
-      <c r="F107" s="31"/>
-      <c r="G107" s="20"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F107" s="22"/>
+      <c r="G107" s="22"/>
+      <c r="H107" s="20"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>96</v>
       </c>
@@ -2042,10 +2149,11 @@
       <c r="C108" s="19"/>
       <c r="D108" s="11"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="31"/>
-      <c r="G108" s="20"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F108" s="22"/>
+      <c r="G108" s="22"/>
+      <c r="H108" s="20"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>97</v>
       </c>
@@ -2053,10 +2161,11 @@
       <c r="C109" s="19"/>
       <c r="D109" s="11"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="31"/>
-      <c r="G109" s="20"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F109" s="22"/>
+      <c r="G109" s="22"/>
+      <c r="H109" s="20"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>98</v>
       </c>
@@ -2064,10 +2173,11 @@
       <c r="C110" s="19"/>
       <c r="D110" s="11"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="31"/>
-      <c r="G110" s="20"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F110" s="22"/>
+      <c r="G110" s="22"/>
+      <c r="H110" s="20"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>99</v>
       </c>
@@ -2075,10 +2185,11 @@
       <c r="C111" s="19"/>
       <c r="D111" s="11"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="31"/>
-      <c r="G111" s="20"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F111" s="22"/>
+      <c r="G111" s="22"/>
+      <c r="H111" s="20"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>100</v>
       </c>
@@ -2086,12 +2197,13 @@
       <c r="C112" s="19"/>
       <c r="D112" s="11"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="20"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="22"/>
+      <c r="H112" s="20"/>
     </row>
     <row r="1048571" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C1048571" s="23"/>
-      <c r="D1048571" s="23"/>
+      <c r="C1048571" s="25"/>
+      <c r="D1048571" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2101,7 +2213,7 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
